--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.63286072228226</v>
+        <v>8.227839867370868</v>
       </c>
       <c r="D2" t="n">
-        <v>28.27729459297551</v>
+        <v>4.59506037135852</v>
       </c>
       <c r="E2" t="n">
-        <v>10.52127096857762</v>
+        <v>1.709706532393864</v>
       </c>
       <c r="F2" t="n">
-        <v>9.84927561443596</v>
+        <v>1.600507287345844</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.73213921133976</v>
+        <v>7.106472621842711</v>
       </c>
       <c r="D3" t="n">
-        <v>49.70160963188214</v>
+        <v>8.076511565180848</v>
       </c>
       <c r="E3" t="n">
-        <v>10.52127096857762</v>
+        <v>1.709706532393864</v>
       </c>
       <c r="F3" t="n">
-        <v>9.84927561443596</v>
+        <v>1.600507287345844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.66263401515994</v>
+        <v>3.35767802746349</v>
       </c>
       <c r="D4" t="n">
-        <v>20.24845673131659</v>
+        <v>3.290374218838946</v>
       </c>
       <c r="E4" t="n">
-        <v>10.52127096857762</v>
+        <v>1.709706532393864</v>
       </c>
       <c r="F4" t="n">
-        <v>9.84927561443596</v>
+        <v>1.600507287345844</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.894781564254</v>
+        <v>5.832902004191276</v>
       </c>
       <c r="D5" t="n">
-        <v>35.2180337927135</v>
+        <v>5.722930491315943</v>
       </c>
       <c r="E5" t="n">
-        <v>10.52127096857762</v>
+        <v>1.709706532393864</v>
       </c>
       <c r="F5" t="n">
-        <v>9.84927561443596</v>
+        <v>1.600507287345844</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.34063835899482</v>
+        <v>4.767853733336659</v>
       </c>
       <c r="D6" t="n">
-        <v>28.77956384878268</v>
+        <v>4.676679125427185</v>
       </c>
       <c r="E6" t="n">
-        <v>10.52127096857762</v>
+        <v>1.709706532393864</v>
       </c>
       <c r="F6" t="n">
-        <v>9.84927561443596</v>
+        <v>1.600507287345844</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
